--- a/data/catalog-entry.xlsx
+++ b/data/catalog-entry.xlsx
@@ -329,7 +329,13 @@
 a wrong value makes a badge unearnable.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional, free text. What the modes actually connect to, e.g. "Walk or boat to EPCOT and Hollywood Studios".
+Fill only where it is not obvious. A value resort whose only mode is bus needs nothing here.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>THE GATE. Format YYYY-MM-DD.
 Rows without it are refused by
@@ -1890,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1899,13 +1905,14 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1941,35 +1948,40 @@
       </c>
       <c r="G1" s="11" t="inlineStr">
         <is>
+          <t>transport_notes</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>official_url</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
@@ -2008,36 +2020,41 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
+          <t>Monorail or boat to Magic Kingdom</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
           <t>28.405000</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>-81.583000</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>https://disneyworld.disney.go.com/resorts/polynesian-resort/</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>Deluxe South Pacific themed resort on the monorail loop.</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr"/>
       <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:M200">
+  <conditionalFormatting sqref="A3:N200">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>AND($A3&lt;&gt;"",$L3="")</formula>
+      <formula>AND($A3&lt;&gt;"",$M3="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -2050,7 +2067,7 @@
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Not a valid value. Pick from the dropdown." promptTitle="" type="list" errorStyle="stop">
       <formula1>=resort_tier</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Not a valid value. Pick from the dropdown." promptTitle="" type="list" errorStyle="stop">
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Not a valid value. Pick from the dropdown." promptTitle="" type="list" errorStyle="stop">
       <formula1>=status</formula1>
     </dataValidation>
   </dataValidations>
